--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -559,13 +559,13 @@
         <v>26681</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>26704</v>
+        <v>24570</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>29545</v>
+        <v>24388</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>34079</v>
+        <v>27512</v>
       </c>
     </row>
     <row r="6">
@@ -599,10 +599,10 @@
         <v>5950</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>7382</v>
+        <v>7226</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>8779</v>
+        <v>8517</v>
       </c>
     </row>
     <row r="7">
@@ -633,13 +633,13 @@
         <v>7628</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>8143</v>
+        <v>7082</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>12293</v>
+        <v>7949</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>20064</v>
+        <v>13882</v>
       </c>
     </row>
     <row r="8">
@@ -670,13 +670,13 @@
         <v>28.2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>26.5</v>
+        <v>30.4</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>17.5</v>
+        <v>27.1</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>10.7</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="9">
@@ -707,13 +707,13 @@
         <v>2.8</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -918,7 +918,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>STB is on the recalculated FinModel_STB_2Q26 (Model!Y121, Y124+Y131, Y144).</t>
+          <t>STB is on FinModel_STB_2Q26 with FY26F loan growth cut to +2.3% (Model!Y121, Y124+Y131, Y144).</t>
         </is>
       </c>
     </row>

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -633,13 +633,13 @@
         <v>7628</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>7082</v>
+        <v>7500</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>7949</v>
+        <v>9973</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>13882</v>
+        <v>16076</v>
       </c>
     </row>
     <row r="8">
@@ -670,13 +670,13 @@
         <v>28.2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>30.4</v>
+        <v>28.7</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>27.1</v>
+        <v>21.6</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>15.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="9">
@@ -713,7 +713,7 @@
         <v>2.3</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -562,10 +562,10 @@
         <v>24570</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>24388</v>
+        <v>28256</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>27512</v>
+        <v>31876</v>
       </c>
     </row>
     <row r="6">
@@ -636,10 +636,10 @@
         <v>7500</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>9973</v>
+        <v>10953</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>16076</v>
+        <v>16448</v>
       </c>
     </row>
     <row r="8">
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>15.8</v>
+        <v>14.6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>28.2</v>
+        <v>26</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>28.7</v>
+        <v>26.5</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>21.6</v>
+        <v>18.1</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>13.4</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="9">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
@@ -939,7 +939,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>P/E and P/B are struck on the target prices used in the August deck: STB VND81,400, FPT VND87,950. Historical years use the same target price, which is how the deck FY tables are built.</t>
+          <t>P/E and P/B are struck on the target prices used in the August deck: STB VND75,000, FPT VND87,950. Historical years use the same target price, which is how the deck FY tables are built.</t>
         </is>
       </c>
     </row>

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -559,13 +559,13 @@
         <v>26681</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>24570</v>
+        <v>24531</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>28256</v>
+        <v>26954</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>31876</v>
+        <v>30600</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>7628</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>7500</v>
+        <v>7461</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>10953</v>
+        <v>9642</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>16448</v>
+        <v>15170</v>
       </c>
     </row>
     <row r="8">
@@ -670,13 +670,13 @@
         <v>26</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>18.1</v>
+        <v>20.6</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +707,7 @@
         <v>2.6</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>2.1</v>

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -636,10 +636,10 @@
         <v>7461</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>9642</v>
+        <v>10872</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>15170</v>
+        <v>17271</v>
       </c>
     </row>
     <row r="8">
@@ -673,10 +673,10 @@
         <v>26.6</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>20.6</v>
+        <v>18.3</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>13.1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="9">

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -636,10 +636,10 @@
         <v>7461</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>10872</v>
+        <v>9872</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>17271</v>
+        <v>16271</v>
       </c>
     </row>
     <row r="8">
@@ -673,10 +673,10 @@
         <v>26.6</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>18.3</v>
+        <v>20.1</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>STB is on FinModel_STB_2Q26 with FY26F loan growth cut to +2.3% (Model!Y121, Y124+Y131, Y144).</t>
+          <t>STB is on FinModel_STB_2Q26 with FY26F loan growth cut to +2.3% (Model!Y121, Y124+Y131, Y144). FY27F and FY28F PBT carry a VND1,000bn provisioning overlay above write-offs (Model!Z278, AA278).</t>
         </is>
       </c>
     </row>

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -639,7 +639,7 @@
         <v>9872</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>16271</v>
+        <v>15271</v>
       </c>
     </row>
     <row r="8">
@@ -676,7 +676,7 @@
         <v>20.1</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -918,7 +918,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>STB is on FinModel_STB_2Q26 with FY26F loan growth cut to +2.3% (Model!Y121, Y124+Y131, Y144). FY27F and FY28F PBT carry a VND1,000bn provisioning overlay above write-offs (Model!Z278, AA278).</t>
+          <t>STB is on FinModel_STB_2Q26 with FY26F loan growth cut to +2.3% (Model!Y121, Y124+Y131, Y144). FY27F PBT carries a VND1,000bn provisioning overlay above write-offs and FY28F VND2,000bn (Model!Z278, AA278).</t>
         </is>
       </c>
     </row>

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -562,7 +562,7 @@
         <v>24531</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>26954</v>
+        <v>26953</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>30600</v>

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>26</v>
+        <v>23.8</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>26.6</v>
+        <v>24.3</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>20.1</v>
+        <v>18.4</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>13</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="9">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10">

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -559,13 +559,13 @@
         <v>26681</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>24531</v>
+        <v>26084</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>26953</v>
+        <v>30380</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>30600</v>
+        <v>34333</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>7628</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>7461</v>
+        <v>7573</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>9872</v>
+        <v>11417</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>15271</v>
+        <v>17229</v>
       </c>
     </row>
     <row r="8">
@@ -670,13 +670,13 @@
         <v>23.8</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>18.4</v>
+        <v>15.9</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>11.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="9">
@@ -713,7 +713,7 @@
         <v>1.9</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10">

--- a/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
+++ b/Mobile_Report_ChartData_STB_FPT_2Q26.xlsx
@@ -559,13 +559,13 @@
         <v>26681</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>26084</v>
+        <v>26098</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>30380</v>
+        <v>30408</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>34333</v>
+        <v>34360</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>7628</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>7573</v>
+        <v>8180</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>11417</v>
+        <v>11433</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>17229</v>
+        <v>17246</v>
       </c>
     </row>
     <row r="8">
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>15.9</v>
+        <v>16.4</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="9">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>2.4</v>
@@ -918,7 +918,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>STB is on FinModel_STB_2Q26 with FY26F loan growth cut to +2.3% (Model!Y121, Y124+Y131, Y144). FY27F PBT carries a VND1,000bn provisioning overlay above write-offs and FY28F VND2,000bn (Model!Z278, AA278).</t>
+          <t>STB is on FinModel_STB_2Q26 with FY26F loan growth of +8.0% (Model!Y121, Y124+Y131, Y144). FY27F PBT carries a VND1,000bn provisioning overlay above write-offs and FY28F VND2,000bn (Model!Z278, AA278).</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>P/E and P/B are struck on the target prices used in the August deck: STB VND75,000, FPT VND87,950. Historical years use the same target price, which is how the deck FY tables are built.</t>
+          <t>P/E and P/B are struck on the target prices used in the August deck: STB VND77,500, FPT VND87,950. Historical years use the same target price, which is how the deck FY tables are built.</t>
         </is>
       </c>
     </row>
